--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$119</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4444" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3772" uniqueCount="355">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,6 +269,10 @@
     <t>*</t>
   </si>
   <si>
+    <t xml:space="preserve">fr-dicom-acte-imagerie-entries:La section contient exactement une entrée Technique d'imagerie (procedure). {entry.where(procedure.exists()).count() = 1}
+</t>
+  </si>
+  <si>
     <t>n/a</t>
   </si>
   <si>
@@ -760,73 +764,36 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomTechniqueImagerie</t>
-  </si>
-  <si>
-    <t>frDicomTechniqueImagerie</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomTechniqueImagerie.nullFlavor</t>
+    <t>Entrée Technique d'imagerie (procedure, 1..1) et entrées Administration de produits (substanceAdministration, 0..*)</t>
   </si>
   <si>
     <t>Section.entry.nullFlavor</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.realmCode</t>
-  </si>
-  <si>
     <t>Section.entry.realmCode</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.typeId</t>
-  </si>
-  <si>
     <t>Section.entry.typeId</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.typeId.nullFlavor</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.nullFlavor</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.assigningAuthorityName</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.typeId.displayable</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.displayable</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.typeId.root</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.root</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.typeId.extension</t>
-  </si>
-  <si>
     <t>Section.entry.typeId.extension</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.templateId</t>
-  </si>
-  <si>
     <t>Section.entry.templateId</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.typeCode</t>
-  </si>
-  <si>
     <t>Section.entry.typeCode</t>
   </si>
   <si>
@@ -839,9 +806,6 @@
     <t>Entry.typeCode</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.contextConductionInd</t>
-  </si>
-  <si>
     <t>Section.entry.contextConductionInd</t>
   </si>
   <si>
@@ -849,9 +813,6 @@
   </si>
   <si>
     <t>Entry.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomTechniqueImagerie.act</t>
   </si>
   <si>
     <t>Section.entry.act</t>
@@ -864,9 +825,6 @@
     <t>Entry.act</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.encounter</t>
-  </si>
-  <si>
     <t>Section.entry.encounter</t>
   </si>
   <si>
@@ -877,9 +835,6 @@
     <t>Entry.encounter</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.observation</t>
-  </si>
-  <si>
     <t>Section.entry.observation</t>
   </si>
   <si>
@@ -890,9 +845,6 @@
     <t>Entry.observation</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.observationMedia</t>
-  </si>
-  <si>
     <t>Section.entry.observationMedia</t>
   </si>
   <si>
@@ -903,9 +855,6 @@
     <t>Entry.observationMedia</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.organizer</t>
-  </si>
-  <si>
     <t>Section.entry.organizer</t>
   </si>
   <si>
@@ -916,9 +865,6 @@
     <t>Entry.organizer</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.procedure</t>
-  </si>
-  <si>
     <t>Section.entry.procedure</t>
   </si>
   <si>
@@ -932,9 +878,6 @@
     <t>Entry.procedure</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.regionOfInterest</t>
-  </si>
-  <si>
     <t>Section.entry.regionOfInterest</t>
   </si>
   <si>
@@ -945,20 +888,17 @@
     <t>Entry.regionOfInterest</t>
   </si>
   <si>
-    <t>Section.entry:frDicomTechniqueImagerie.substanceAdministration</t>
-  </si>
-  <si>
     <t>Section.entry.substanceAdministration</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/SubstanceAdministration
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/SubstanceAdministration {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-administration-produit-de-sante|0.1.0}
 </t>
   </si>
   <si>
+    <t>Entrée Administration de produits</t>
+  </si>
+  <si>
     <t>Entry.substanceAdministration</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomTechniqueImagerie.supply</t>
   </si>
   <si>
     <t>Section.entry.supply</t>
@@ -971,83 +911,6 @@
     <t>Entry.supply</t>
   </si>
   <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante</t>
-  </si>
-  <si>
-    <t>frDicomAdministrationProduitDeSante</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.realmCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.typeId</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.typeId.nullFlavor</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.typeId.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.typeId.displayable</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.typeId.root</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.typeId.extension</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.templateId</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.typeCode</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.contextConductionInd</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.act</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.encounter</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.observation</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.observationMedia</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.organizer</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.procedure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Procedure
-</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.regionOfInterest</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.substanceAdministration</t>
-  </si>
-  <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/SubstanceAdministration {https://interop.esante.gouv.fr/ig/cda/document-core/StructureDefinition/fr-cda-dicom-administration-produit-de-sante|0.1.0}
-</t>
-  </si>
-  <si>
-    <t>Entrée Administration de produits</t>
-  </si>
-  <si>
-    <t>Section.entry:frDicomAdministrationProduitDeSante.supply</t>
-  </si>
-  <si>
     <t>Section.component</t>
   </si>
   <si>
@@ -1062,6 +925,10 @@
   </si>
   <si>
     <t>Context propagates to nested sections</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile:section}
+</t>
   </si>
   <si>
     <t>Section.component.nullFlavor</t>
@@ -1568,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK141"/>
+  <dimension ref="A1:AK119"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="73.4765625" customWidth="true" bestFit="true"/>
@@ -1819,25 +1686,25 @@
         <v>75</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F3" t="s" s="2">
         <v>81</v>
@@ -1855,11 +1722,11 @@
         <v>75</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -1886,11 +1753,11 @@
         <v>75</v>
       </c>
       <c r="X3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y3" s="2"/>
       <c r="Z3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA3" t="s" s="2">
         <v>75</v>
@@ -1908,7 +1775,7 @@
         <v>75</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>81</v>
@@ -1928,10 +1795,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1954,11 +1821,11 @@
         <v>75</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -2009,7 +1876,7 @@
         <v>75</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>81</v>
@@ -2029,10 +1896,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -2055,11 +1922,11 @@
         <v>75</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -2110,7 +1977,7 @@
         <v>75</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>81</v>
@@ -2122,7 +1989,7 @@
         <v>75</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>75</v>
@@ -2130,17 +1997,17 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E6" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F6" t="s" s="2">
         <v>81</v>
@@ -2158,11 +2025,11 @@
         <v>75</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -2189,11 +2056,11 @@
         <v>75</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y6" s="2"/>
       <c r="Z6" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>75</v>
@@ -2211,7 +2078,7 @@
         <v>75</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>81</v>
@@ -2231,17 +2098,17 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>81</v>
@@ -2259,11 +2126,11 @@
         <v>75</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2314,7 +2181,7 @@
         <v>75</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>81</v>
@@ -2334,17 +2201,17 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>81</v>
@@ -2362,11 +2229,11 @@
         <v>75</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2417,7 +2284,7 @@
         <v>75</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>81</v>
@@ -2437,17 +2304,17 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>76</v>
@@ -2465,11 +2332,11 @@
         <v>75</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2478,7 +2345,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>75</v>
@@ -2520,7 +2387,7 @@
         <v>75</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>81</v>
@@ -2540,17 +2407,17 @@
     </row>
     <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>76</v>
@@ -2568,11 +2435,11 @@
         <v>75</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2623,7 +2490,7 @@
         <v>75</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>81</v>
@@ -2643,10 +2510,10 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2654,10 +2521,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>75</v>
@@ -2669,11 +2536,11 @@
         <v>75</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2712,17 +2579,17 @@
         <v>75</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AC11" s="2"/>
       <c r="AD11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>81</v>
@@ -2742,13 +2609,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>75</v>
@@ -2770,13 +2637,13 @@
         <v>75</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2827,7 +2694,7 @@
         <v>75</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -2847,17 +2714,17 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E13" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F13" t="s" s="2">
         <v>81</v>
@@ -2875,11 +2742,11 @@
         <v>75</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L13" s="2"/>
       <c r="M13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2906,11 +2773,11 @@
         <v>75</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>75</v>
@@ -2928,7 +2795,7 @@
         <v>75</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -2948,17 +2815,17 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E14" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F14" t="s" s="2">
         <v>81</v>
@@ -2976,11 +2843,11 @@
         <v>75</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L14" s="2"/>
       <c r="M14" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3031,7 +2898,7 @@
         <v>75</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3051,17 +2918,17 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E15" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F15" t="s" s="2">
         <v>81</v>
@@ -3079,11 +2946,11 @@
         <v>75</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L15" s="2"/>
       <c r="M15" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -3134,7 +3001,7 @@
         <v>75</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3154,17 +3021,17 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>76</v>
@@ -3182,11 +3049,11 @@
         <v>75</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3198,7 +3065,7 @@
         <v>75</v>
       </c>
       <c r="S16" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="T16" t="s" s="2">
         <v>75</v>
@@ -3237,7 +3104,7 @@
         <v>75</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3257,17 +3124,17 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F17" t="s" s="2">
         <v>81</v>
@@ -3285,11 +3152,11 @@
         <v>75</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L17" s="2"/>
       <c r="M17" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3340,7 +3207,7 @@
         <v>75</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -3360,13 +3227,13 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C18" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D18" t="s" s="2">
         <v>75</v>
@@ -3388,13 +3255,13 @@
         <v>75</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3445,7 +3312,7 @@
         <v>75</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -3465,17 +3332,17 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>81</v>
@@ -3493,11 +3360,11 @@
         <v>75</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3524,11 +3391,11 @@
         <v>75</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y19" s="2"/>
       <c r="Z19" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>75</v>
@@ -3546,7 +3413,7 @@
         <v>75</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -3566,17 +3433,17 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>81</v>
@@ -3594,11 +3461,11 @@
         <v>75</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3649,7 +3516,7 @@
         <v>75</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -3669,17 +3536,17 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>81</v>
@@ -3697,11 +3564,11 @@
         <v>75</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3752,7 +3619,7 @@
         <v>75</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -3772,17 +3639,17 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E22" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F22" t="s" s="2">
         <v>76</v>
@@ -3800,11 +3667,11 @@
         <v>75</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3816,7 +3683,7 @@
         <v>75</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>75</v>
@@ -3855,7 +3722,7 @@
         <v>75</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -3875,17 +3742,17 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>81</v>
@@ -3903,11 +3770,11 @@
         <v>75</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3958,7 +3825,7 @@
         <v>75</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -3978,10 +3845,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4004,10 +3871,10 @@
         <v>75</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
@@ -4059,7 +3926,7 @@
         <v>75</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4079,10 +3946,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4105,7 +3972,7 @@
         <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -4116,7 +3983,7 @@
       </c>
       <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S25" t="s" s="2">
         <v>75</v>
@@ -4134,11 +4001,11 @@
         <v>75</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>75</v>
@@ -4156,7 +4023,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -4176,10 +4043,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4202,7 +4069,7 @@
         <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -4213,7 +4080,7 @@
       </c>
       <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="S26" t="s" s="2">
         <v>75</v>
@@ -4231,11 +4098,11 @@
         <v>75</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y26" s="2"/>
       <c r="Z26" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>75</v>
@@ -4253,7 +4120,7 @@
         <v>75</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -4273,10 +4140,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4290,7 +4157,7 @@
         <v>76</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>75</v>
@@ -4299,13 +4166,13 @@
         <v>75</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4356,7 +4223,7 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -4376,10 +4243,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4393,7 +4260,7 @@
         <v>76</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>75</v>
@@ -4402,13 +4269,13 @@
         <v>75</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4459,7 +4326,7 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -4479,17 +4346,17 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>81</v>
@@ -4507,11 +4374,11 @@
         <v>75</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4538,11 +4405,11 @@
         <v>75</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y29" s="2"/>
       <c r="Z29" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
@@ -4560,7 +4427,7 @@
         <v>75</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -4580,10 +4447,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4608,11 +4475,11 @@
         <v>75</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4624,7 +4491,7 @@
         <v>75</v>
       </c>
       <c r="S30" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="T30" t="s" s="2">
         <v>75</v>
@@ -4663,7 +4530,7 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -4683,17 +4550,17 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>76</v>
@@ -4711,11 +4578,11 @@
         <v>75</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4727,7 +4594,7 @@
         <v>75</v>
       </c>
       <c r="S31" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="T31" t="s" s="2">
         <v>75</v>
@@ -4766,7 +4633,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -4786,17 +4653,17 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>81</v>
@@ -4814,11 +4681,11 @@
         <v>75</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4830,7 +4697,7 @@
         <v>75</v>
       </c>
       <c r="S32" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="T32" t="s" s="2">
         <v>75</v>
@@ -4869,7 +4736,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -4889,17 +4756,17 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F33" t="s" s="2">
         <v>81</v>
@@ -4917,11 +4784,11 @@
         <v>75</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4972,7 +4839,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -4992,17 +4859,17 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E34" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="F34" t="s" s="2">
         <v>76</v>
@@ -5020,11 +4887,11 @@
         <v>75</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5036,7 +4903,7 @@
         <v>75</v>
       </c>
       <c r="S34" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="T34" t="s" s="2">
         <v>75</v>
@@ -5075,7 +4942,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -5095,10 +4962,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5121,11 +4988,11 @@
         <v>75</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5176,7 +5043,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -5196,10 +5063,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5222,11 +5089,11 @@
         <v>75</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5277,7 +5144,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -5297,17 +5164,17 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>81</v>
@@ -5325,11 +5192,11 @@
         <v>75</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5380,7 +5247,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -5400,17 +5267,17 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E38" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F38" t="s" s="2">
         <v>81</v>
@@ -5428,11 +5295,11 @@
         <v>75</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L38" s="2"/>
       <c r="M38" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -5483,7 +5350,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -5503,17 +5370,17 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E39" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F39" t="s" s="2">
         <v>81</v>
@@ -5531,11 +5398,11 @@
         <v>75</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="L39" s="2"/>
       <c r="M39" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -5586,7 +5453,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -5606,10 +5473,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5623,7 +5490,7 @@
         <v>76</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>75</v>
@@ -5632,17 +5499,17 @@
         <v>75</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>75</v>
@@ -5691,7 +5558,7 @@
         <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -5711,10 +5578,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5728,7 +5595,7 @@
         <v>76</v>
       </c>
       <c r="H41" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I41" t="s" s="2">
         <v>75</v>
@@ -5737,16 +5604,16 @@
         <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -5796,7 +5663,7 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -5816,10 +5683,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5842,15 +5709,15 @@
         <v>75</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M42" s="2"/>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>75</v>
@@ -5899,7 +5766,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -5919,10 +5786,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5945,15 +5812,15 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>75</v>
@@ -5978,11 +5845,11 @@
         <v>75</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="Y43" s="2"/>
       <c r="Z43" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>75</v>
@@ -6000,7 +5867,7 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -6020,10 +5887,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6046,17 +5913,17 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M44" s="2"/>
       <c r="N44" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>75</v>
@@ -6105,7 +5972,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -6125,10 +5992,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6151,13 +6018,13 @@
         <v>75</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>75</v>
@@ -6206,7 +6073,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -6226,10 +6093,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6252,13 +6119,13 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6307,7 +6174,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -6325,12 +6192,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="47" hidden="true">
+    <row r="47">
       <c r="A47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6344,7 +6211,7 @@
         <v>82</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>75</v>
@@ -6353,9 +6220,11 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>239</v>
-      </c>
-      <c r="L47" s="2"/>
+        <v>240</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>241</v>
+      </c>
       <c r="M47" s="2"/>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -6394,17 +6263,19 @@
         <v>75</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AC47" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC47" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD47" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -6424,20 +6295,20 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C48" t="s" s="2">
         <v>242</v>
       </c>
+      <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E48" s="2"/>
+      <c r="E48" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F48" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>76</v>
@@ -6452,10 +6323,12 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>239</v>
+        <v>87</v>
       </c>
       <c r="L48" s="2"/>
-      <c r="M48" s="2"/>
+      <c r="M48" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
@@ -6481,13 +6354,11 @@
         <v>75</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y48" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y48" s="2"/>
       <c r="Z48" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>75</v>
@@ -6505,13 +6376,13 @@
         <v>75</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>238</v>
+        <v>91</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>75</v>
@@ -6528,20 +6399,18 @@
         <v>243</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E49" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>75</v>
@@ -6553,11 +6422,11 @@
         <v>75</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L49" s="2"/>
       <c r="M49" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6584,11 +6453,13 @@
         <v>75</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y49" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y49" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z49" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>75</v>
@@ -6606,13 +6477,13 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>75</v>
@@ -6626,10 +6497,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6640,7 +6511,7 @@
         <v>81</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>75</v>
@@ -6652,11 +6523,11 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L50" s="2"/>
       <c r="M50" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -6707,19 +6578,19 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK50" t="s" s="2">
         <v>75</v>
@@ -6727,16 +6598,18 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E51" s="2"/>
+      <c r="E51" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F51" t="s" s="2">
         <v>81</v>
       </c>
@@ -6753,11 +6626,11 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6784,13 +6657,11 @@
         <v>75</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y51" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y51" s="2"/>
       <c r="Z51" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>75</v>
@@ -6808,7 +6679,7 @@
         <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -6820,7 +6691,7 @@
         <v>75</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>75</v>
@@ -6828,17 +6699,17 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E52" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F52" t="s" s="2">
         <v>81</v>
@@ -6856,11 +6727,11 @@
         <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6887,11 +6758,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y52" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y52" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z52" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -6909,7 +6782,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -6929,17 +6802,17 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E53" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F53" t="s" s="2">
         <v>81</v>
@@ -6957,11 +6830,11 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -7012,7 +6885,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -7032,20 +6905,20 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F54" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
         <v>76</v>
@@ -7060,11 +6933,11 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -7073,7 +6946,7 @@
       </c>
       <c r="Q54" s="2"/>
       <c r="R54" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S54" t="s" s="2">
         <v>75</v>
@@ -7115,7 +6988,7 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -7135,17 +7008,17 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E55" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F55" t="s" s="2">
         <v>76</v>
@@ -7163,11 +7036,11 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -7176,7 +7049,7 @@
       </c>
       <c r="Q55" s="2"/>
       <c r="R55" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S55" t="s" s="2">
         <v>75</v>
@@ -7218,7 +7091,7 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -7238,23 +7111,21 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E56" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>75</v>
@@ -7266,11 +7137,11 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L56" s="2"/>
       <c r="M56" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -7321,13 +7192,13 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>75</v>
@@ -7341,10 +7212,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7355,7 +7226,7 @@
         <v>81</v>
       </c>
       <c r="G57" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H57" t="s" s="2">
         <v>75</v>
@@ -7367,16 +7238,14 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L57" s="2"/>
-      <c r="M57" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M57" s="2"/>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="Q57" s="2"/>
       <c r="R57" t="s" s="2">
@@ -7398,13 +7267,11 @@
         <v>75</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y57" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>75</v>
+        <v>253</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>75</v>
@@ -7422,13 +7289,13 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>126</v>
+        <v>254</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH57" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI57" t="s" s="2">
         <v>75</v>
@@ -7442,10 +7309,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7468,18 +7335,18 @@
         <v>75</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="Q58" s="2"/>
       <c r="R58" t="s" s="2">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="S58" t="s" s="2">
         <v>75</v>
@@ -7497,11 +7364,13 @@
         <v>75</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y58" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y58" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z58" t="s" s="2">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>75</v>
@@ -7519,7 +7388,7 @@
         <v>75</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -7539,10 +7408,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7565,7 +7434,7 @@
         <v>75</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>108</v>
+        <v>259</v>
       </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
@@ -7576,7 +7445,7 @@
       </c>
       <c r="Q59" s="2"/>
       <c r="R59" t="s" s="2">
-        <v>268</v>
+        <v>75</v>
       </c>
       <c r="S59" t="s" s="2">
         <v>75</v>
@@ -7618,7 +7487,7 @@
         <v>75</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -7638,10 +7507,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7664,7 +7533,7 @@
         <v>75</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
@@ -7717,7 +7586,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -7737,10 +7606,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7763,7 +7632,7 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
@@ -7816,7 +7685,7 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -7836,10 +7705,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>279</v>
+        <v>267</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7862,7 +7731,7 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
@@ -7915,7 +7784,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -7935,10 +7804,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>282</v>
+        <v>270</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>283</v>
+        <v>270</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7961,7 +7830,7 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>284</v>
+        <v>271</v>
       </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
@@ -8014,7 +7883,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>285</v>
+        <v>272</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -8034,10 +7903,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>286</v>
+        <v>273</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8060,9 +7929,11 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>288</v>
-      </c>
-      <c r="L64" s="2"/>
+        <v>274</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="M64" s="2"/>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8113,7 +7984,7 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -8133,10 +8004,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -8159,11 +8030,9 @@
         <v>75</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="L65" t="s" s="2">
-        <v>293</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="L65" s="2"/>
       <c r="M65" s="2"/>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -8214,7 +8083,7 @@
         <v>75</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>294</v>
+        <v>279</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -8234,10 +8103,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -8260,9 +8129,11 @@
         <v>75</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="L66" s="2"/>
+        <v>281</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>282</v>
+      </c>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8313,7 +8184,7 @@
         <v>75</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -8333,10 +8204,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -8359,7 +8230,7 @@
         <v>75</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>301</v>
+        <v>285</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
@@ -8412,7 +8283,7 @@
         <v>75</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>302</v>
+        <v>286</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -8432,10 +8303,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>303</v>
+        <v>287</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>304</v>
+        <v>287</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8443,13 +8314,13 @@
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s" s="2">
-        <v>76</v>
+        <v>288</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>75</v>
+        <v>162</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
@@ -8458,12 +8329,16 @@
         <v>75</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="L68" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="M68" s="2"/>
       <c r="N68" s="2"/>
-      <c r="O68" s="2"/>
+      <c r="O68" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P68" t="s" s="2">
         <v>75</v>
       </c>
@@ -8499,25 +8374,23 @@
         <v>75</v>
       </c>
       <c r="AB68" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC68" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>292</v>
+      </c>
+      <c r="AC68" s="2"/>
       <c r="AD68" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE68" t="s" s="2">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH68" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI68" t="s" s="2">
         <v>75</v>
@@ -8531,23 +8404,23 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="C69" t="s" s="2">
-        <v>308</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E69" s="2"/>
+      <c r="E69" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G69" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H69" t="s" s="2">
         <v>75</v>
@@ -8559,10 +8432,12 @@
         <v>75</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>239</v>
+        <v>87</v>
       </c>
       <c r="L69" s="2"/>
-      <c r="M69" s="2"/>
+      <c r="M69" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -8588,13 +8463,11 @@
         <v>75</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y69" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>75</v>
@@ -8612,13 +8485,13 @@
         <v>75</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>238</v>
+        <v>91</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH69" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI69" t="s" s="2">
         <v>75</v>
@@ -8632,23 +8505,21 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>244</v>
+        <v>294</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E70" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G70" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H70" t="s" s="2">
         <v>75</v>
@@ -8660,11 +8531,11 @@
         <v>75</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="L70" s="2"/>
       <c r="M70" t="s" s="2">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -8691,11 +8562,13 @@
         <v>75</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y70" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z70" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>75</v>
@@ -8713,13 +8586,13 @@
         <v>75</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH70" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI70" t="s" s="2">
         <v>75</v>
@@ -8733,10 +8606,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>310</v>
+        <v>295</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>246</v>
+        <v>295</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8747,7 +8620,7 @@
         <v>81</v>
       </c>
       <c r="G71" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H71" t="s" s="2">
         <v>75</v>
@@ -8759,11 +8632,11 @@
         <v>75</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="L71" s="2"/>
       <c r="M71" t="s" s="2">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -8814,19 +8687,19 @@
         <v>75</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH71" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI71" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ71" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK71" t="s" s="2">
         <v>75</v>
@@ -8834,16 +8707,18 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>248</v>
+        <v>296</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E72" s="2"/>
+      <c r="E72" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F72" t="s" s="2">
         <v>81</v>
       </c>
@@ -8860,11 +8735,11 @@
         <v>75</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8891,13 +8766,11 @@
         <v>75</v>
       </c>
       <c r="X72" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y72" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y72" s="2"/>
       <c r="Z72" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA72" t="s" s="2">
         <v>75</v>
@@ -8915,7 +8788,7 @@
         <v>75</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -8927,7 +8800,7 @@
         <v>75</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>75</v>
@@ -8935,17 +8808,17 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>312</v>
+        <v>297</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>250</v>
+        <v>297</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E73" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="F73" t="s" s="2">
         <v>81</v>
@@ -8963,11 +8836,11 @@
         <v>75</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8994,11 +8867,13 @@
         <v>75</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y73" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z73" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>75</v>
@@ -9016,7 +8891,7 @@
         <v>75</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -9036,17 +8911,17 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>252</v>
+        <v>298</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E74" t="s" s="2">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F74" t="s" s="2">
         <v>81</v>
@@ -9064,11 +8939,11 @@
         <v>75</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="L74" s="2"/>
       <c r="M74" t="s" s="2">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -9119,7 +8994,7 @@
         <v>75</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -9139,20 +9014,20 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>254</v>
+        <v>299</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E75" t="s" s="2">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="F75" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s" s="2">
         <v>76</v>
@@ -9167,11 +9042,11 @@
         <v>75</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L75" s="2"/>
       <c r="M75" t="s" s="2">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9180,7 +9055,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>75</v>
@@ -9222,7 +9097,7 @@
         <v>75</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -9242,17 +9117,17 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>315</v>
+        <v>300</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>256</v>
+        <v>300</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E76" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F76" t="s" s="2">
         <v>76</v>
@@ -9270,11 +9145,11 @@
         <v>75</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" t="s" s="2">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -9283,7 +9158,7 @@
       </c>
       <c r="Q76" s="2"/>
       <c r="R76" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S76" t="s" s="2">
         <v>75</v>
@@ -9325,7 +9200,7 @@
         <v>75</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -9345,23 +9220,21 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>316</v>
+        <v>301</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>258</v>
+        <v>301</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E77" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>75</v>
@@ -9373,11 +9246,11 @@
         <v>75</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="L77" s="2"/>
       <c r="M77" t="s" s="2">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -9428,13 +9301,13 @@
         <v>75</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>75</v>
@@ -9448,10 +9321,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>260</v>
+        <v>302</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9462,7 +9335,7 @@
         <v>81</v>
       </c>
       <c r="G78" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H78" t="s" s="2">
         <v>75</v>
@@ -9474,11 +9347,11 @@
         <v>75</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="L78" s="2"/>
       <c r="M78" t="s" s="2">
-        <v>123</v>
+        <v>303</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -9487,7 +9360,7 @@
       </c>
       <c r="Q78" s="2"/>
       <c r="R78" t="s" s="2">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="S78" t="s" s="2">
         <v>75</v>
@@ -9529,13 +9402,13 @@
         <v>75</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>126</v>
+        <v>302</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH78" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI78" t="s" s="2">
         <v>75</v>
@@ -9549,10 +9422,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>318</v>
+        <v>304</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>262</v>
+        <v>304</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9575,18 +9448,18 @@
         <v>75</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="Q79" s="2"/>
       <c r="R79" t="s" s="2">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="S79" t="s" s="2">
         <v>75</v>
@@ -9604,11 +9477,13 @@
         <v>75</v>
       </c>
       <c r="X79" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y79" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z79" t="s" s="2">
-        <v>264</v>
+        <v>75</v>
       </c>
       <c r="AA79" t="s" s="2">
         <v>75</v>
@@ -9626,7 +9501,7 @@
         <v>75</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>265</v>
+        <v>304</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -9646,10 +9521,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>319</v>
+        <v>305</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>267</v>
+        <v>305</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -9657,7 +9532,7 @@
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s" s="2">
         <v>76</v>
@@ -9672,7 +9547,7 @@
         <v>75</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>108</v>
+        <v>306</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
@@ -9683,7 +9558,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>268</v>
+        <v>75</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>75</v>
@@ -9725,10 +9600,10 @@
         <v>75</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>269</v>
+        <v>305</v>
       </c>
       <c r="AG80" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH80" t="s" s="2">
         <v>76</v>
@@ -9745,12 +9620,14 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="C81" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="C81" t="s" s="2">
+        <v>308</v>
+      </c>
       <c r="D81" t="s" s="2">
         <v>75</v>
       </c>
@@ -9771,12 +9648,16 @@
         <v>75</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>272</v>
-      </c>
-      <c r="L81" s="2"/>
+        <v>289</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>290</v>
+      </c>
       <c r="M81" s="2"/>
       <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
+      <c r="O81" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P81" t="s" s="2">
         <v>75</v>
       </c>
@@ -9824,13 +9705,13 @@
         <v>75</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>75</v>
@@ -9844,16 +9725,18 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E82" s="2"/>
+      <c r="E82" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F82" t="s" s="2">
         <v>81</v>
       </c>
@@ -9870,10 +9753,12 @@
         <v>75</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>276</v>
+        <v>87</v>
       </c>
       <c r="L82" s="2"/>
-      <c r="M82" s="2"/>
+      <c r="M82" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -9899,13 +9784,11 @@
         <v>75</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y82" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>75</v>
@@ -9923,7 +9806,7 @@
         <v>75</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>277</v>
+        <v>91</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -9943,10 +9826,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>322</v>
+        <v>310</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -9957,7 +9840,7 @@
         <v>81</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>75</v>
@@ -9969,10 +9852,12 @@
         <v>75</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>280</v>
+        <v>93</v>
       </c>
       <c r="L83" s="2"/>
-      <c r="M83" s="2"/>
+      <c r="M83" t="s" s="2">
+        <v>94</v>
+      </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
@@ -10022,13 +9907,13 @@
         <v>75</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>281</v>
+        <v>95</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH83" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI83" t="s" s="2">
         <v>75</v>
@@ -10042,10 +9927,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>323</v>
+        <v>311</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>283</v>
+        <v>295</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -10068,10 +9953,12 @@
         <v>75</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>284</v>
+        <v>97</v>
       </c>
       <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
+      <c r="M84" t="s" s="2">
+        <v>98</v>
+      </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -10121,7 +10008,7 @@
         <v>75</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>285</v>
+        <v>99</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -10133,7 +10020,7 @@
         <v>75</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>75</v>
@@ -10141,16 +10028,18 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>324</v>
+        <v>312</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E85" s="2"/>
+      <c r="E85" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="F85" t="s" s="2">
         <v>81</v>
       </c>
@@ -10167,10 +10056,12 @@
         <v>75</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>288</v>
+        <v>87</v>
       </c>
       <c r="L85" s="2"/>
-      <c r="M85" s="2"/>
+      <c r="M85" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -10196,13 +10087,11 @@
         <v>75</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y85" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y85" s="2"/>
       <c r="Z85" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>75</v>
@@ -10220,7 +10109,7 @@
         <v>75</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>289</v>
+        <v>91</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -10240,16 +10129,18 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E86" s="2"/>
+      <c r="E86" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="F86" t="s" s="2">
         <v>81</v>
       </c>
@@ -10266,10 +10157,12 @@
         <v>75</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>326</v>
+        <v>104</v>
       </c>
       <c r="L86" s="2"/>
-      <c r="M86" s="2"/>
+      <c r="M86" t="s" s="2">
+        <v>105</v>
+      </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -10319,7 +10212,7 @@
         <v>75</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>294</v>
+        <v>106</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -10339,16 +10232,18 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E87" s="2"/>
+      <c r="E87" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="F87" t="s" s="2">
         <v>81</v>
       </c>
@@ -10365,10 +10260,12 @@
         <v>75</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>297</v>
+        <v>109</v>
       </c>
       <c r="L87" s="2"/>
-      <c r="M87" s="2"/>
+      <c r="M87" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -10418,7 +10315,7 @@
         <v>75</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>298</v>
+        <v>111</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -10438,18 +10335,20 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E88" s="2"/>
+      <c r="E88" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="F88" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G88" t="s" s="2">
         <v>76</v>
@@ -10464,12 +10363,12 @@
         <v>75</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="L88" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="M88" s="2"/>
+        <v>114</v>
+      </c>
+      <c r="L88" s="2"/>
+      <c r="M88" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -10477,7 +10376,7 @@
       </c>
       <c r="Q88" s="2"/>
       <c r="R88" t="s" s="2">
-        <v>75</v>
+        <v>116</v>
       </c>
       <c r="S88" t="s" s="2">
         <v>75</v>
@@ -10519,7 +10418,7 @@
         <v>75</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>302</v>
+        <v>117</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>81</v>
@@ -10539,18 +10438,20 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E89" s="2"/>
+      <c r="E89" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="F89" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s" s="2">
         <v>76</v>
@@ -10565,10 +10466,12 @@
         <v>75</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>305</v>
+        <v>104</v>
       </c>
       <c r="L89" s="2"/>
-      <c r="M89" s="2"/>
+      <c r="M89" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -10618,7 +10521,7 @@
         <v>75</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>306</v>
+        <v>121</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -10638,10 +10541,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>332</v>
+        <v>301</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10649,13 +10552,13 @@
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G90" t="s" s="2">
-        <v>333</v>
+        <v>82</v>
       </c>
       <c r="H90" t="s" s="2">
-        <v>161</v>
+        <v>75</v>
       </c>
       <c r="I90" t="s" s="2">
         <v>75</v>
@@ -10664,16 +10567,14 @@
         <v>75</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M90" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="L90" s="2"/>
+      <c r="M90" t="s" s="2">
+        <v>124</v>
+      </c>
       <c r="N90" s="2"/>
-      <c r="O90" t="s" s="2">
-        <v>336</v>
-      </c>
+      <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>75</v>
       </c>
@@ -10709,17 +10610,19 @@
         <v>75</v>
       </c>
       <c r="AB90" t="s" s="2">
-        <v>240</v>
-      </c>
-      <c r="AC90" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD90" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE90" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>332</v>
+        <v>127</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -10739,18 +10642,16 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>337</v>
+        <v>318</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E91" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>81</v>
       </c>
@@ -10767,11 +10668,11 @@
         <v>75</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L91" s="2"/>
       <c r="M91" t="s" s="2">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -10780,7 +10681,7 @@
       </c>
       <c r="Q91" s="2"/>
       <c r="R91" t="s" s="2">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="S91" t="s" s="2">
         <v>75</v>
@@ -10798,11 +10699,13 @@
         <v>75</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y91" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z91" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>75</v>
@@ -10820,7 +10723,7 @@
         <v>75</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>90</v>
+        <v>302</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -10840,10 +10743,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>338</v>
+        <v>319</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10854,7 +10757,7 @@
         <v>81</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>75</v>
@@ -10866,12 +10769,10 @@
         <v>75</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="L92" s="2"/>
-      <c r="M92" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M92" s="2"/>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
       <c r="P92" t="s" s="2">
@@ -10879,7 +10780,7 @@
       </c>
       <c r="Q92" s="2"/>
       <c r="R92" t="s" s="2">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="S92" t="s" s="2">
         <v>75</v>
@@ -10921,13 +10822,13 @@
         <v>75</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>94</v>
+        <v>304</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI92" t="s" s="2">
         <v>75</v>
@@ -10941,10 +10842,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10952,7 +10853,7 @@
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G93" t="s" s="2">
         <v>76</v>
@@ -10967,12 +10868,12 @@
         <v>75</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L93" s="2"/>
-      <c r="M93" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>321</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
@@ -11022,10 +10923,10 @@
         <v>75</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>98</v>
+        <v>305</v>
       </c>
       <c r="AG93" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH93" t="s" s="2">
         <v>76</v>
@@ -11034,7 +10935,7 @@
         <v>75</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>75</v>
@@ -11042,18 +10943,18 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>340</v>
+        <v>323</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>287</v>
+      </c>
+      <c r="C94" t="s" s="2">
+        <v>324</v>
+      </c>
       <c r="D94" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E94" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
         <v>81</v>
       </c>
@@ -11070,14 +10971,16 @@
         <v>75</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L94" s="2"/>
-      <c r="M94" t="s" s="2">
-        <v>87</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M94" s="2"/>
       <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
+      <c r="O94" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>75</v>
       </c>
@@ -11101,11 +11004,13 @@
         <v>75</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y94" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z94" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>75</v>
@@ -11123,13 +11028,13 @@
         <v>75</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>90</v>
+        <v>287</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH94" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI94" t="s" s="2">
         <v>75</v>
@@ -11143,17 +11048,17 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E95" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F95" t="s" s="2">
         <v>81</v>
@@ -11171,11 +11076,11 @@
         <v>75</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="L95" s="2"/>
       <c r="M95" t="s" s="2">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -11202,13 +11107,11 @@
         <v>75</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y95" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y95" s="2"/>
       <c r="Z95" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>75</v>
@@ -11226,7 +11129,7 @@
         <v>75</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -11246,23 +11149,21 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>342</v>
+        <v>326</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E96" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G96" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H96" t="s" s="2">
         <v>75</v>
@@ -11274,11 +11175,11 @@
         <v>75</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="L96" s="2"/>
       <c r="M96" t="s" s="2">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -11329,13 +11230,13 @@
         <v>75</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH96" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI96" t="s" s="2">
         <v>75</v>
@@ -11349,20 +11250,18 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>343</v>
+        <v>327</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E97" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G97" t="s" s="2">
         <v>76</v>
@@ -11377,11 +11276,11 @@
         <v>75</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="L97" s="2"/>
       <c r="M97" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -11390,7 +11289,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>75</v>
@@ -11432,7 +11331,7 @@
         <v>75</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -11444,7 +11343,7 @@
         <v>75</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>75</v>
@@ -11452,20 +11351,20 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E98" t="s" s="2">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="F98" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G98" t="s" s="2">
         <v>76</v>
@@ -11480,11 +11379,11 @@
         <v>75</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="L98" s="2"/>
       <c r="M98" t="s" s="2">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -11511,13 +11410,11 @@
         <v>75</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y98" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y98" s="2"/>
       <c r="Z98" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>75</v>
@@ -11535,7 +11432,7 @@
         <v>75</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -11555,21 +11452,23 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>345</v>
+        <v>329</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="F99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G99" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H99" t="s" s="2">
         <v>75</v>
@@ -11581,11 +11480,11 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11636,13 +11535,13 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>75</v>
@@ -11656,16 +11555,18 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>346</v>
+        <v>330</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E100" s="2"/>
+      <c r="E100" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="F100" t="s" s="2">
         <v>81</v>
       </c>
@@ -11682,11 +11583,11 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -11695,7 +11596,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>75</v>
@@ -11737,7 +11638,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>346</v>
+        <v>111</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -11757,18 +11658,20 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>348</v>
+        <v>331</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E101" s="2"/>
+      <c r="E101" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="F101" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G101" t="s" s="2">
         <v>76</v>
@@ -11783,10 +11686,12 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L101" s="2"/>
-      <c r="M101" s="2"/>
+      <c r="M101" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -11794,7 +11699,7 @@
       </c>
       <c r="Q101" s="2"/>
       <c r="R101" t="s" s="2">
-        <v>268</v>
+        <v>116</v>
       </c>
       <c r="S101" t="s" s="2">
         <v>75</v>
@@ -11836,7 +11741,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>348</v>
+        <v>117</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -11856,16 +11761,18 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>349</v>
+        <v>332</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E102" s="2"/>
+      <c r="E102" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="F102" t="s" s="2">
         <v>76</v>
       </c>
@@ -11882,10 +11789,12 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>350</v>
+        <v>104</v>
       </c>
       <c r="L102" s="2"/>
-      <c r="M102" s="2"/>
+      <c r="M102" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -11935,10 +11844,10 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>349</v>
+        <v>121</v>
       </c>
       <c r="AG102" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH102" t="s" s="2">
         <v>76</v>
@@ -11955,14 +11864,12 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>351</v>
+        <v>333</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C103" t="s" s="2">
-        <v>352</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
@@ -11971,7 +11878,7 @@
         <v>81</v>
       </c>
       <c r="G103" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H103" t="s" s="2">
         <v>75</v>
@@ -11983,16 +11890,14 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M103" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="L103" s="2"/>
+      <c r="M103" t="s" s="2">
+        <v>124</v>
+      </c>
       <c r="N103" s="2"/>
-      <c r="O103" t="s" s="2">
-        <v>336</v>
-      </c>
+      <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
         <v>75</v>
       </c>
@@ -12040,7 +11945,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>332</v>
+        <v>127</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12060,18 +11965,16 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>353</v>
+        <v>334</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E104" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E104" s="2"/>
       <c r="F104" t="s" s="2">
         <v>81</v>
       </c>
@@ -12088,11 +11991,11 @@
         <v>75</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12101,7 +12004,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>75</v>
@@ -12119,11 +12022,13 @@
         <v>75</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y104" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z104" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>75</v>
@@ -12141,7 +12046,7 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>90</v>
+        <v>302</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -12161,10 +12066,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>354</v>
+        <v>335</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -12175,7 +12080,7 @@
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>75</v>
@@ -12187,12 +12092,10 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="L105" s="2"/>
-      <c r="M105" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -12200,7 +12103,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>75</v>
@@ -12242,13 +12145,13 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>94</v>
+        <v>304</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>75</v>
@@ -12262,10 +12165,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>355</v>
+        <v>336</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -12273,7 +12176,7 @@
       </c>
       <c r="E106" s="2"/>
       <c r="F106" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G106" t="s" s="2">
         <v>76</v>
@@ -12288,12 +12191,12 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L106" s="2"/>
-      <c r="M106" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="M106" s="2"/>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -12343,10 +12246,10 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>98</v>
+        <v>305</v>
       </c>
       <c r="AG106" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH106" t="s" s="2">
         <v>76</v>
@@ -12355,7 +12258,7 @@
         <v>75</v>
       </c>
       <c r="AJ106" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK106" t="s" s="2">
         <v>75</v>
@@ -12363,20 +12266,20 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>356</v>
+        <v>339</v>
       </c>
       <c r="B107" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="C107" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E107" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E107" s="2"/>
       <c r="F107" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G107" t="s" s="2">
         <v>76</v>
@@ -12391,14 +12294,16 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L107" s="2"/>
-      <c r="M107" t="s" s="2">
-        <v>87</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>290</v>
+      </c>
+      <c r="M107" s="2"/>
       <c r="N107" s="2"/>
-      <c r="O107" s="2"/>
+      <c r="O107" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="P107" t="s" s="2">
         <v>75</v>
       </c>
@@ -12422,11 +12327,13 @@
         <v>75</v>
       </c>
       <c r="X107" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y107" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z107" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA107" t="s" s="2">
         <v>75</v>
@@ -12444,13 +12351,13 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>90</v>
+        <v>287</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH107" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI107" t="s" s="2">
         <v>75</v>
@@ -12464,17 +12371,17 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>341</v>
+        <v>293</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="F108" t="s" s="2">
         <v>81</v>
@@ -12492,11 +12399,11 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>104</v>
+        <v>88</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12523,13 +12430,11 @@
         <v>75</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y108" s="2"/>
       <c r="Z108" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>75</v>
@@ -12547,7 +12452,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>105</v>
+        <v>91</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -12567,23 +12472,21 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>358</v>
+        <v>342</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>342</v>
+        <v>294</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E109" t="s" s="2">
-        <v>107</v>
-      </c>
+      <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H109" t="s" s="2">
         <v>75</v>
@@ -12595,11 +12498,11 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -12650,13 +12553,13 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH109" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI109" t="s" s="2">
         <v>75</v>
@@ -12670,20 +12573,18 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>359</v>
+        <v>343</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>343</v>
+        <v>295</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E110" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>76</v>
@@ -12698,11 +12599,11 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>113</v>
+        <v>97</v>
       </c>
       <c r="L110" s="2"/>
       <c r="M110" t="s" s="2">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -12711,7 +12612,7 @@
       </c>
       <c r="Q110" s="2"/>
       <c r="R110" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S110" t="s" s="2">
         <v>75</v>
@@ -12753,7 +12654,7 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -12765,7 +12666,7 @@
         <v>75</v>
       </c>
       <c r="AJ110" t="s" s="2">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="AK110" t="s" s="2">
         <v>75</v>
@@ -12773,20 +12674,20 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>360</v>
+        <v>344</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>344</v>
+        <v>296</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E111" t="s" s="2">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="F111" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>76</v>
@@ -12801,11 +12702,11 @@
         <v>75</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="L111" s="2"/>
       <c r="M111" t="s" s="2">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
@@ -12832,13 +12733,11 @@
         <v>75</v>
       </c>
       <c r="X111" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -12856,7 +12755,7 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>120</v>
+        <v>91</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -12876,21 +12775,23 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E112" s="2"/>
+      <c r="E112" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="F112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G112" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H112" t="s" s="2">
         <v>75</v>
@@ -12902,11 +12803,11 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>96</v>
+        <v>104</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" t="s" s="2">
-        <v>123</v>
+        <v>105</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -12957,13 +12858,13 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>126</v>
+        <v>106</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH112" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI112" t="s" s="2">
         <v>75</v>
@@ -12977,16 +12878,18 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>346</v>
+        <v>298</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E113" s="2"/>
+      <c r="E113" t="s" s="2">
+        <v>108</v>
+      </c>
       <c r="F113" t="s" s="2">
         <v>81</v>
       </c>
@@ -13003,11 +12906,11 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>86</v>
+        <v>109</v>
       </c>
       <c r="L113" s="2"/>
       <c r="M113" t="s" s="2">
-        <v>347</v>
+        <v>110</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -13016,7 +12919,7 @@
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" t="s" s="2">
-        <v>263</v>
+        <v>75</v>
       </c>
       <c r="S113" t="s" s="2">
         <v>75</v>
@@ -13058,7 +12961,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>346</v>
+        <v>111</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13078,18 +12981,20 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>363</v>
+        <v>347</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>348</v>
+        <v>299</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>113</v>
+      </c>
       <c r="F114" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G114" t="s" s="2">
         <v>76</v>
@@ -13104,10 +13009,12 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="L114" s="2"/>
-      <c r="M114" s="2"/>
+      <c r="M114" t="s" s="2">
+        <v>115</v>
+      </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
       <c r="P114" t="s" s="2">
@@ -13115,7 +13022,7 @@
       </c>
       <c r="Q114" s="2"/>
       <c r="R114" t="s" s="2">
-        <v>268</v>
+        <v>116</v>
       </c>
       <c r="S114" t="s" s="2">
         <v>75</v>
@@ -13157,7 +13064,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>348</v>
+        <v>117</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13177,16 +13084,18 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>364</v>
+        <v>348</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>349</v>
+        <v>300</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E115" s="2"/>
+      <c r="E115" t="s" s="2">
+        <v>119</v>
+      </c>
       <c r="F115" t="s" s="2">
         <v>76</v>
       </c>
@@ -13203,12 +13112,12 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>365</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="M115" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="L115" s="2"/>
+      <c r="M115" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -13258,10 +13167,10 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>349</v>
+        <v>121</v>
       </c>
       <c r="AG115" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH115" t="s" s="2">
         <v>76</v>
@@ -13278,14 +13187,12 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>367</v>
+        <v>349</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C116" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>301</v>
+      </c>
+      <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
         <v>75</v>
       </c>
@@ -13294,7 +13201,7 @@
         <v>81</v>
       </c>
       <c r="G116" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H116" t="s" s="2">
         <v>75</v>
@@ -13306,16 +13213,14 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M116" s="2"/>
+        <v>97</v>
+      </c>
+      <c r="L116" s="2"/>
+      <c r="M116" t="s" s="2">
+        <v>124</v>
+      </c>
       <c r="N116" s="2"/>
-      <c r="O116" t="s" s="2">
-        <v>336</v>
-      </c>
+      <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
         <v>75</v>
       </c>
@@ -13363,7 +13268,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>332</v>
+        <v>127</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -13383,18 +13288,16 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>369</v>
+        <v>350</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E117" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
         <v>81</v>
       </c>
@@ -13411,11 +13314,11 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>87</v>
+        <v>303</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
@@ -13424,7 +13327,7 @@
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
-        <v>75</v>
+        <v>252</v>
       </c>
       <c r="S117" t="s" s="2">
         <v>75</v>
@@ -13442,11 +13345,13 @@
         <v>75</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y117" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z117" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>75</v>
@@ -13464,7 +13369,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>90</v>
+        <v>302</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -13484,10 +13389,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>370</v>
+        <v>351</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>338</v>
+        <v>304</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -13498,7 +13403,7 @@
         <v>81</v>
       </c>
       <c r="G118" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H118" t="s" s="2">
         <v>75</v>
@@ -13510,12 +13415,10 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="L118" s="2"/>
-      <c r="M118" t="s" s="2">
-        <v>93</v>
-      </c>
+      <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" t="s" s="2">
@@ -13523,7 +13426,7 @@
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" t="s" s="2">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="S118" t="s" s="2">
         <v>75</v>
@@ -13565,13 +13468,13 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>94</v>
+        <v>304</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH118" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI118" t="s" s="2">
         <v>75</v>
@@ -13585,10 +13488,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>371</v>
+        <v>352</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>339</v>
+        <v>305</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -13596,7 +13499,7 @@
       </c>
       <c r="E119" s="2"/>
       <c r="F119" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G119" t="s" s="2">
         <v>76</v>
@@ -13611,12 +13514,12 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L119" s="2"/>
-      <c r="M119" t="s" s="2">
-        <v>97</v>
-      </c>
+        <v>353</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>354</v>
+      </c>
+      <c r="M119" s="2"/>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" t="s" s="2">
@@ -13666,10 +13569,10 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>98</v>
+        <v>305</v>
       </c>
       <c r="AG119" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH119" t="s" s="2">
         <v>76</v>
@@ -13678,2252 +13581,14 @@
         <v>75</v>
       </c>
       <c r="AJ119" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK119" t="s" s="2">
         <v>75</v>
       </c>
     </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E120" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L120" s="2"/>
-      <c r="M120" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N120" s="2"/>
-      <c r="O120" s="2"/>
-      <c r="P120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y120" s="2"/>
-      <c r="Z120" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E121" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L121" s="2"/>
-      <c r="M121" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N121" s="2"/>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E122" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L122" s="2"/>
-      <c r="M122" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E123" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L123" s="2"/>
-      <c r="M123" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E124" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L124" s="2"/>
-      <c r="M124" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="125" hidden="true">
-      <c r="A125" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="B125" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C125" s="2"/>
-      <c r="D125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E125" s="2"/>
-      <c r="F125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K125" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L125" s="2"/>
-      <c r="M125" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q125" s="2"/>
-      <c r="R125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF125" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG125" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH125" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ125" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK125" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="126" hidden="true">
-      <c r="A126" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="B126" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C126" s="2"/>
-      <c r="D126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E126" s="2"/>
-      <c r="F126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G126" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K126" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L126" s="2"/>
-      <c r="M126" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q126" s="2"/>
-      <c r="R126" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="S126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF126" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AG126" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH126" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ126" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK126" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="127" hidden="true">
-      <c r="A127" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B127" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C127" s="2"/>
-      <c r="D127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E127" s="2"/>
-      <c r="F127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K127" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L127" s="2"/>
-      <c r="M127" s="2"/>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q127" s="2"/>
-      <c r="R127" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="S127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF127" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AG127" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH127" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK127" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="128" hidden="true">
-      <c r="A128" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B128" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C128" s="2"/>
-      <c r="D128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E128" s="2"/>
-      <c r="F128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K128" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="L128" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q128" s="2"/>
-      <c r="R128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF128" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AG128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH128" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ128" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK128" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="129" hidden="true">
-      <c r="A129" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="B129" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="C129" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="D129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E129" s="2"/>
-      <c r="F129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G129" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K129" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="L129" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
-      <c r="O129" t="s" s="2">
-        <v>336</v>
-      </c>
-      <c r="P129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q129" s="2"/>
-      <c r="R129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF129" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="AG129" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH129" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ129" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK129" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="130" hidden="true">
-      <c r="A130" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="B130" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="C130" s="2"/>
-      <c r="D130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E130" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K130" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L130" s="2"/>
-      <c r="M130" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q130" s="2"/>
-      <c r="R130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X130" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y130" s="2"/>
-      <c r="Z130" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF130" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG130" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH130" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ130" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK130" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="131" hidden="true">
-      <c r="A131" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B131" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C131" s="2"/>
-      <c r="D131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E131" s="2"/>
-      <c r="F131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K131" t="s" s="2">
-        <v>92</v>
-      </c>
-      <c r="L131" s="2"/>
-      <c r="M131" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q131" s="2"/>
-      <c r="R131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF131" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AG131" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH131" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ131" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK131" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="132" hidden="true">
-      <c r="A132" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="B132" t="s" s="2">
-        <v>339</v>
-      </c>
-      <c r="C132" s="2"/>
-      <c r="D132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E132" s="2"/>
-      <c r="F132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G132" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K132" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L132" s="2"/>
-      <c r="M132" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q132" s="2"/>
-      <c r="R132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF132" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AG132" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH132" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ132" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK132" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="133" hidden="true">
-      <c r="A133" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="B133" t="s" s="2">
-        <v>340</v>
-      </c>
-      <c r="C133" s="2"/>
-      <c r="D133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E133" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="F133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K133" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L133" s="2"/>
-      <c r="M133" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q133" s="2"/>
-      <c r="R133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X133" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y133" s="2"/>
-      <c r="Z133" t="s" s="2">
-        <v>89</v>
-      </c>
-      <c r="AA133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF133" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="AG133" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH133" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK133" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="134" hidden="true">
-      <c r="A134" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="B134" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C134" s="2"/>
-      <c r="D134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E134" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="F134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G134" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K134" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L134" s="2"/>
-      <c r="M134" t="s" s="2">
-        <v>104</v>
-      </c>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q134" s="2"/>
-      <c r="R134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF134" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="AG134" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH134" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ134" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK134" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="135" hidden="true">
-      <c r="A135" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="B135" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="C135" s="2"/>
-      <c r="D135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E135" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="F135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K135" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L135" s="2"/>
-      <c r="M135" t="s" s="2">
-        <v>109</v>
-      </c>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q135" s="2"/>
-      <c r="R135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF135" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="AG135" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH135" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ135" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK135" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="136" hidden="true">
-      <c r="A136" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="B136" t="s" s="2">
-        <v>343</v>
-      </c>
-      <c r="C136" s="2"/>
-      <c r="D136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E136" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="F136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K136" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L136" s="2"/>
-      <c r="M136" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q136" s="2"/>
-      <c r="R136" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="S136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF136" t="s" s="2">
-        <v>116</v>
-      </c>
-      <c r="AG136" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH136" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ136" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK136" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="137" hidden="true">
-      <c r="A137" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="B137" t="s" s="2">
-        <v>344</v>
-      </c>
-      <c r="C137" s="2"/>
-      <c r="D137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E137" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K137" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L137" s="2"/>
-      <c r="M137" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q137" s="2"/>
-      <c r="R137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF137" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="AG137" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH137" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ137" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK137" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="138" hidden="true">
-      <c r="A138" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B138" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="C138" s="2"/>
-      <c r="D138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E138" s="2"/>
-      <c r="F138" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K138" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L138" s="2"/>
-      <c r="M138" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q138" s="2"/>
-      <c r="R138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF138" t="s" s="2">
-        <v>126</v>
-      </c>
-      <c r="AG138" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH138" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ138" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK138" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="139" hidden="true">
-      <c r="A139" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="B139" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="C139" s="2"/>
-      <c r="D139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E139" s="2"/>
-      <c r="F139" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G139" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K139" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L139" s="2"/>
-      <c r="M139" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-      <c r="P139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q139" s="2"/>
-      <c r="R139" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="S139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF139" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="AG139" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH139" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK139" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="140" hidden="true">
-      <c r="A140" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="B140" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="C140" s="2"/>
-      <c r="D140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E140" s="2"/>
-      <c r="F140" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K140" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="L140" s="2"/>
-      <c r="M140" s="2"/>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
-      <c r="P140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q140" s="2"/>
-      <c r="R140" t="s" s="2">
-        <v>268</v>
-      </c>
-      <c r="S140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF140" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="AG140" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH140" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ140" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK140" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="141" hidden="true">
-      <c r="A141" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="B141" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="C141" s="2"/>
-      <c r="D141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E141" s="2"/>
-      <c r="F141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="G141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K141" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="L141" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="M141" s="2"/>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-      <c r="P141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q141" s="2"/>
-      <c r="R141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF141" t="s" s="2">
-        <v>349</v>
-      </c>
-      <c r="AG141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH141" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ141" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK141" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AK141">
+  <autoFilter ref="A1:AK119">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -15933,7 +13598,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI140">
+  <conditionalFormatting sqref="A2:AI118">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-dicom-acte-imagerie.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
